--- a/analysis/nts_distributions/analysis.xlsx
+++ b/analysis/nts_distributions/analysis.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="19029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://transportsystemscatapult-my.sharepoint.com/personal/haris_ballis_ts_catapult_org_uk/Documents/Research/PhD/Models/tripchains_from_ODs/nts_distributions/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ucy-my.sharepoint.com/personal/tballi01_ucy_ac_cy/Documents/Tools/od2trs/analysis/nts_distributions/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30074186-FA83-4263-A060-8F11AB60E29C}" xr6:coauthVersionLast="28" xr6:coauthVersionMax="28" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{30074186-FA83-4263-A060-8F11AB60E29C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{38B8FF56-61DE-4C5A-9B3E-F638B06EEF07}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12210" xr2:uid="{1764C3A8-9644-48AE-ABE4-57DF6A4536D3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1764C3A8-9644-48AE-ABE4-57DF6A4536D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="171027"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId2"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -82,6 +82,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0000%"/>
+  </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -111,7 +114,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -121,11 +124,98 @@
       <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="28">
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.0000%"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -202,6 +292,47 @@
         <c:marker>
           <c:symbol val="none"/>
         </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -3225,7 +3356,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{779394B3-29BB-426C-A040-D72A61A85F88}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{779394B3-29BB-426C-A040-D72A61A85F88}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="6" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="H2:I22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField showAll="0">
@@ -3349,6 +3480,108 @@
   <dataFields count="1">
     <dataField name="Sum of Percentage" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
+  <formats count="9">
+    <format dxfId="17">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="15">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="13">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+          <reference field="3" count="4">
+            <x v="0"/>
+            <x v="1"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="11">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="9">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+          <reference field="3" count="3">
+            <x v="1"/>
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="7">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="5">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+          <reference field="3" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="3">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="2" count="1">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="1">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+          <reference field="3" count="2">
+            <x v="3"/>
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <chartFormats count="1">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
@@ -3375,12 +3608,15 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{8B162540-0288-4C31-857C-DFB7D72B5E83}" name="Table1" displayName="Table1" ref="B2:F286" totalsRowShown="0">
   <autoFilter ref="B2:F286" xr:uid="{72B2ADB3-E551-403C-880A-0BE4624BC862}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:F286">
+    <sortCondition descending="1" ref="F2:F286"/>
+  </sortState>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{066FFB4B-8A44-4E35-B183-895A43AFF1CF}" name="NumStages"/>
     <tableColumn id="2" xr3:uid="{10E32B57-E2F6-4ABE-ACCE-363C26EF0B1A}" name="Distance"/>
     <tableColumn id="3" xr3:uid="{79BD5AE5-5CD3-4E21-A8F7-049CDBDB7DA2}" name="TripStart"/>
     <tableColumn id="4" xr3:uid="{C3BDD7A7-F881-4C05-AE8E-B0987AE061CC}" name="TripEnd"/>
-    <tableColumn id="5" xr3:uid="{7654B9C1-CDF2-4887-82B1-0FAE14F17A29}" name="Percentage"/>
+    <tableColumn id="5" xr3:uid="{7654B9C1-CDF2-4887-82B1-0FAE14F17A29}" name="Percentage" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3726,13 +3962,13 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>9.0753251991529697E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.124735303015024</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>6</v>
@@ -3747,18 +3983,18 @@
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4">
-        <v>3.83180397297569E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F4" s="5">
+        <v>6.5947363113844901E-2</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="4">
+      <c r="I4" s="6">
         <v>5.0418473328627516E-3</v>
       </c>
     </row>
@@ -3770,18 +4006,18 @@
         <v>5</v>
       </c>
       <c r="D5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5">
-        <v>1.03862055056972E-2</v>
+        <v>9</v>
+      </c>
+      <c r="F5" s="5">
+        <v>6.1107189674296597E-2</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="4">
+      <c r="I5" s="6">
         <v>2.9847736210547416E-2</v>
       </c>
     </row>
@@ -3793,18 +4029,18 @@
         <v>5</v>
       </c>
       <c r="D6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
-      <c r="F6">
-        <v>9.9828577190682593E-3</v>
+      <c r="F6" s="5">
+        <v>4.7494201875567202E-2</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="4">
+      <c r="I6" s="6">
         <v>1.310880306544317E-3</v>
       </c>
     </row>
@@ -3816,18 +4052,18 @@
         <v>5</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
-      <c r="F7">
-        <v>3.73096702631844E-3</v>
+      <c r="F7" s="5">
+        <v>3.3982051023494997E-2</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I7" s="4">
+      <c r="I7" s="6">
         <v>4.1645658969446303E-2</v>
       </c>
     </row>
@@ -3836,21 +4072,21 @@
         <v>2</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8">
-        <v>2.5612584450942801E-2</v>
+        <v>9</v>
+      </c>
+      <c r="F8" s="5">
+        <v>3.31753554502369E-2</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="4">
+      <c r="I8" s="6">
         <v>2.8839366743974953E-2</v>
       </c>
     </row>
@@ -3865,19 +4101,19 @@
         <v>7</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9">
-        <v>6.5947363113844901E-2</v>
+        <v>7</v>
+      </c>
+      <c r="F9" s="5">
+        <v>2.5612584450942801E-2</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I9" s="4"/>
+      <c r="I9" s="6"/>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
@@ -3886,15 +4122,15 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10">
-        <v>6.1107189674296597E-2</v>
+        <v>8</v>
+      </c>
+      <c r="F10" s="5">
+        <v>2.3797519411112199E-2</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I10" s="4">
+      <c r="I10" s="6">
         <v>2.984773621054751E-2</v>
       </c>
     </row>
@@ -3906,18 +4142,18 @@
         <v>5</v>
       </c>
       <c r="D11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11">
-        <v>9.1761621458102197E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F11" s="5">
+        <v>2.2990823837854099E-2</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="4">
+      <c r="I11" s="6">
         <v>0.15478471311888661</v>
       </c>
     </row>
@@ -3929,18 +4165,18 @@
         <v>5</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12">
-        <v>0.124735303015024</v>
+        <v>10</v>
+      </c>
+      <c r="F12" s="5">
+        <v>2.2385802157910601E-2</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="4">
+      <c r="I12" s="6">
         <v>0.17938892810325674</v>
       </c>
     </row>
@@ -3949,21 +4185,21 @@
         <v>2</v>
       </c>
       <c r="C13" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D13" t="s">
         <v>8</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13">
-        <v>4.7494201875567202E-2</v>
+        <v>8</v>
+      </c>
+      <c r="F13" s="5">
+        <v>1.7545628718362401E-2</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I13" s="4">
+      <c r="I13" s="6">
         <v>8.440052435212253E-2</v>
       </c>
     </row>
@@ -3972,88 +4208,88 @@
         <v>2</v>
       </c>
       <c r="C14" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14">
-        <v>1.38146616920439E-2</v>
+        <v>8</v>
+      </c>
+      <c r="F14" s="5">
+        <v>1.6839770091761599E-2</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="4"/>
+      <c r="I14" s="6"/>
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C15" t="s">
         <v>5</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E15" t="s">
         <v>9</v>
       </c>
-      <c r="F15">
-        <v>2.2990823837854099E-2</v>
+      <c r="F15" s="5">
+        <v>1.61339114651608E-2</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="4">
+      <c r="I15" s="6">
         <v>0.1755571241302806</v>
       </c>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C16" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16">
-        <v>3.3982051023494997E-2</v>
+        <v>9</v>
+      </c>
+      <c r="F16" s="5">
+        <v>1.5932237571846301E-2</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I16" s="4">
+      <c r="I16" s="6">
         <v>0.10103862055056967</v>
       </c>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C17" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D17" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
       </c>
-      <c r="F17">
-        <v>2.2385802157910601E-2</v>
+      <c r="F17" s="5">
+        <v>1.52263789452455E-2</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I17" s="4">
+      <c r="I17" s="6">
         <v>6.1006352727639261E-2</v>
       </c>
     </row>
@@ -4062,21 +4298,21 @@
         <v>2</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D18" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18">
-        <v>3.0251083997176502E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F18" s="5">
+        <v>1.38146616920439E-2</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="I18" s="4"/>
+      <c r="I18" s="6"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B19">
@@ -4089,15 +4325,15 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19">
-        <v>4.0334778662901998E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F19" s="5">
+        <v>1.36129877987294E-2</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I19" s="4">
+      <c r="I19" s="6">
         <v>2.7931834224059631E-2</v>
       </c>
     </row>
@@ -4109,62 +4345,62 @@
         <v>11</v>
       </c>
       <c r="D20" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20">
-        <v>8.2686296258949205E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F20" s="5">
+        <v>1.35121508520722E-2</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="I20" s="4"/>
+      <c r="I20" s="6"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>2</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
-      </c>
-      <c r="F21">
-        <v>1.36129877987294E-2</v>
+        <v>8</v>
+      </c>
+      <c r="F21" s="5">
+        <v>1.03862055056972E-2</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="I21" s="4">
+      <c r="I21" s="6">
         <v>2.6116769184229002E-2</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B22">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
       <c r="D22" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
-      <c r="F22">
-        <v>6.9577493193506102E-3</v>
+      <c r="F22" s="5">
+        <v>1.00836946657255E-2</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I22" s="4">
+      <c r="I22" s="6">
         <v>5.3241907835030688E-2</v>
       </c>
     </row>
@@ -4173,16 +4409,16 @@
         <v>2</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23">
-        <v>2.4200867197741202E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F23" s="5">
+        <v>9.9828577190682593E-3</v>
       </c>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
@@ -4196,15 +4432,15 @@
         <v>7</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24">
-        <v>1.6839770091761599E-2</v>
+        <v>10</v>
+      </c>
+      <c r="F24" s="5">
+        <v>9.9828577190682593E-3</v>
       </c>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B25">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
@@ -4213,27 +4449,27 @@
         <v>7</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25">
-        <v>3.31753554502369E-2</v>
+        <v>8</v>
+      </c>
+      <c r="F25" s="5">
+        <v>9.9828577190682593E-3</v>
       </c>
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D26" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26">
-        <v>9.9828577190682593E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F26" s="5">
+        <v>9.7811838257537507E-3</v>
       </c>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
@@ -4247,10 +4483,10 @@
         <v>8</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27">
-        <v>1.7545628718362401E-2</v>
+        <v>10</v>
+      </c>
+      <c r="F27" s="5">
+        <v>9.4786729857819895E-3</v>
       </c>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
@@ -4258,16 +4494,16 @@
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D28" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28">
-        <v>1.35121508520722E-2</v>
+        <v>10</v>
+      </c>
+      <c r="F28" s="5">
+        <v>9.1761621458102197E-3</v>
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
@@ -4278,47 +4514,47 @@
         <v>11</v>
       </c>
       <c r="D29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
-      <c r="F29">
-        <v>9.4786729857819895E-3</v>
+      <c r="F29" s="5">
+        <v>9.0753251991529602E-3</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
-      </c>
-      <c r="F30">
-        <v>1.00836946657255E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F30" s="5">
+        <v>8.7728143591812007E-3</v>
       </c>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
-      </c>
-      <c r="F31">
-        <v>9.0753251991529602E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F31" s="5">
+        <v>8.5711404658666904E-3</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.25">
@@ -4329,64 +4565,64 @@
         <v>11</v>
       </c>
       <c r="D32" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32">
-        <v>4.0334778662901999E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F32" s="5">
+        <v>8.2686296258949205E-3</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D33" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33">
-        <v>1.0083694665725499E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F33" s="5">
+        <v>7.8652818392658998E-3</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D34" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
-      <c r="F34">
-        <v>2.2184128264596099E-3</v>
+      <c r="F34" s="5">
+        <v>7.3610971059796301E-3</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D35" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E35" t="s">
         <v>9</v>
       </c>
-      <c r="F35">
-        <v>4.6384995462337396E-3</v>
+      <c r="F35" s="5">
+        <v>7.2602601593223697E-3</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
@@ -4394,7 +4630,7 @@
         <v>2</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D36" t="s">
         <v>6</v>
@@ -4402,50 +4638,50 @@
       <c r="E36" t="s">
         <v>10</v>
       </c>
-      <c r="F36">
-        <v>4.2351517596047102E-3</v>
+      <c r="F36" s="5">
+        <v>6.9577493193506102E-3</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D37" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F37">
-        <v>2.3192497731168698E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F37" s="5">
+        <v>6.1510537460925602E-3</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D38" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38">
-        <v>4.7393364928909904E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F38" s="5">
+        <v>6.1510537460925602E-3</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B39">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D39" t="s">
         <v>7</v>
@@ -4453,16 +4689,16 @@
       <c r="E39" t="s">
         <v>10</v>
       </c>
-      <c r="F39">
-        <v>3.5292931330039301E-3</v>
+      <c r="F39" s="5">
+        <v>6.1510537460925602E-3</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D40" t="s">
         <v>8</v>
@@ -4470,127 +4706,127 @@
       <c r="E40" t="s">
         <v>8</v>
       </c>
-      <c r="F40">
-        <v>2.0167389331450999E-3</v>
+      <c r="F40" s="5">
+        <v>5.9493798527780499E-3</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D41" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
       </c>
-      <c r="F41">
-        <v>2.4200867197741202E-3</v>
+      <c r="F41" s="5">
+        <v>5.8485429061207999E-3</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C42" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D42" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42">
-        <v>3.0251083997176499E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F42" s="5">
+        <v>5.7477059594635404E-3</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B43">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C43" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D43" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F43" s="5">
+        <v>5.6468690128062904E-3</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B44">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C44" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D44" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E44" t="s">
-        <v>10</v>
-      </c>
-      <c r="F44">
-        <v>1.2100433598870601E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F44" s="5">
+        <v>5.54603206614903E-3</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B45">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D45" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45">
-        <v>4.0334778662901998E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F45" s="5">
+        <v>5.4451951194917801E-3</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B46">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C46" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46">
-        <v>1.0083694665725499E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F46" s="5">
+        <v>5.4451951194917801E-3</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B47">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C47" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F47" s="5">
+        <v>5.1426842795200102E-3</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
@@ -4598,16 +4834,16 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D48" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" t="s">
         <v>9</v>
       </c>
-      <c r="F48">
-        <v>5.0418473328627596E-4</v>
+      <c r="F48" s="5">
+        <v>4.7393364928909904E-3</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
@@ -4615,33 +4851,33 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D49" t="s">
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49">
-        <v>1.0083694665725499E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F49" s="5">
+        <v>4.6384995462337396E-3</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B50">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C50" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D50" t="s">
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>8</v>
-      </c>
-      <c r="F50">
-        <v>3.0251083997176502E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F50" s="5">
+        <v>4.4368256529192197E-3</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
@@ -4649,33 +4885,33 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51">
-        <v>5.0418473328627596E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F51" s="5">
+        <v>4.2351517596047102E-3</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B52">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C52" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D52" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
-      <c r="F52">
-        <v>7.0585862660078598E-4</v>
+      <c r="F52" s="5">
+        <v>4.1343148129474603E-3</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
@@ -4683,55 +4919,55 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D53" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53">
-        <v>4.0334778662901998E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F53" s="5">
+        <v>4.0334778662901999E-3</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B54">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D54" t="s">
         <v>8</v>
       </c>
       <c r="E54" t="s">
-        <v>10</v>
-      </c>
-      <c r="F54">
-        <v>9.0753251991529697E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F54" s="5">
+        <v>4.0334778662901999E-3</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B55">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C55" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D55" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
-      </c>
-      <c r="F55">
-        <v>3.0251083997176502E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F55" s="5">
+        <v>3.9326409196329499E-3</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C56" t="s">
         <v>5</v>
@@ -4740,15 +4976,15 @@
         <v>6</v>
       </c>
       <c r="E56" t="s">
-        <v>8</v>
-      </c>
-      <c r="F56">
-        <v>3.0251083997176502E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F56" s="5">
+        <v>3.83180397297569E-3</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B57">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="s">
         <v>5</v>
@@ -4757,10 +4993,10 @@
         <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
-      </c>
-      <c r="F57">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F57" s="5">
+        <v>3.73096702631844E-3</v>
       </c>
     </row>
     <row r="58" spans="2:6" x14ac:dyDescent="0.25">
@@ -4768,75 +5004,75 @@
         <v>3</v>
       </c>
       <c r="C58" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D58" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
-      <c r="F58">
-        <v>4.0334778662901998E-4</v>
+      <c r="F58" s="5">
+        <v>3.73096702631844E-3</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B59">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
-        <v>7</v>
-      </c>
-      <c r="F59">
-        <v>6.0502167994353102E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F59" s="5">
+        <v>3.73096702631844E-3</v>
       </c>
     </row>
     <row r="60" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D60" t="s">
         <v>7</v>
       </c>
       <c r="E60" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60">
-        <v>8.7728143591812007E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F60" s="5">
+        <v>3.5292931330039301E-3</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B61">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C61" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D61" t="s">
         <v>7</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61">
-        <v>5.8485429061207999E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F61" s="5">
+        <v>3.5292931330039301E-3</v>
       </c>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B62">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C62" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D62" t="s">
         <v>7</v>
@@ -4844,234 +5080,234 @@
       <c r="E62" t="s">
         <v>10</v>
       </c>
-      <c r="F62">
-        <v>1.91590198648784E-3</v>
+      <c r="F62" s="5">
+        <v>3.3276192396894202E-3</v>
       </c>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B63">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D63" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
-      <c r="F63">
-        <v>9.7811838257537507E-3</v>
+      <c r="F63" s="5">
+        <v>3.2267822930321598E-3</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B64">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D64" t="s">
         <v>8</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64">
-        <v>6.1510537460925602E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F64" s="5">
+        <v>3.2267822930321598E-3</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B65">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C65" t="s">
         <v>5</v>
       </c>
       <c r="D65" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65">
-        <v>1.1092064132297999E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F65" s="5">
+        <v>3.2267822930321598E-3</v>
       </c>
     </row>
     <row r="66" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B66">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C66" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D66" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E66" t="s">
         <v>9</v>
       </c>
-      <c r="F66">
-        <v>1.3108803065443101E-3</v>
+      <c r="F66" s="5">
+        <v>3.1259453463749099E-3</v>
       </c>
     </row>
     <row r="67" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D67" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
-      <c r="F67">
-        <v>1.7142280931733301E-3</v>
+      <c r="F67" s="5">
+        <v>3.0251083997176499E-3</v>
       </c>
     </row>
     <row r="68" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B68">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C68" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D68" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68">
-        <v>5.0418473328627596E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F68" s="5">
+        <v>2.9242714530603999E-3</v>
       </c>
     </row>
     <row r="69" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B69">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D69" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E69" t="s">
-        <v>7</v>
-      </c>
-      <c r="F69">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F69" s="5">
+        <v>2.9242714530603999E-3</v>
       </c>
     </row>
     <row r="70" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B70">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D70" t="s">
         <v>6</v>
       </c>
       <c r="E70" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70">
-        <v>1.41171725320157E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F70" s="5">
+        <v>2.72259755974589E-3</v>
       </c>
     </row>
     <row r="71" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B71">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D71" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71">
-        <v>1.41171725320157E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F71" s="5">
+        <v>2.6217606130886301E-3</v>
       </c>
     </row>
     <row r="72" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" t="s">
         <v>11</v>
       </c>
       <c r="D72" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E72" t="s">
-        <v>10</v>
-      </c>
-      <c r="F72">
-        <v>1.00836946657255E-3</v>
+        <v>7</v>
+      </c>
+      <c r="F72" s="5">
+        <v>2.4200867197741202E-3</v>
       </c>
     </row>
     <row r="73" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D73" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E73" t="s">
-        <v>8</v>
-      </c>
-      <c r="F73">
-        <v>5.7477059594635404E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F73" s="5">
+        <v>2.4200867197741202E-3</v>
       </c>
     </row>
     <row r="74" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D74" t="s">
         <v>7</v>
       </c>
       <c r="E74" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74">
-        <v>7.8652818392658998E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F74" s="5">
+        <v>2.3192497731168698E-3</v>
       </c>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B75">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C75" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D75" t="s">
         <v>7</v>
       </c>
       <c r="E75" t="s">
-        <v>10</v>
-      </c>
-      <c r="F75">
-        <v>3.73096702631844E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F75" s="5">
+        <v>2.3192497731168698E-3</v>
       </c>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B76">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C76" t="s">
         <v>11</v>
@@ -5080,44 +5316,44 @@
         <v>8</v>
       </c>
       <c r="E76" t="s">
-        <v>8</v>
-      </c>
-      <c r="F76">
-        <v>5.9493798527780499E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F76" s="5">
+        <v>2.3192497731168698E-3</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D77" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77">
-        <v>5.4451951194917801E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F77" s="5">
+        <v>2.2184128264596099E-3</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C78" t="s">
         <v>11</v>
       </c>
       <c r="D78" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>10</v>
-      </c>
-      <c r="F78">
-        <v>2.1175758798023499E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F78" s="5">
+        <v>2.2184128264596099E-3</v>
       </c>
     </row>
     <row r="79" spans="2:6" x14ac:dyDescent="0.25">
@@ -5128,47 +5364,47 @@
         <v>11</v>
       </c>
       <c r="D79" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F79" s="5">
+        <v>2.1175758798023499E-3</v>
       </c>
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C80" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
-      </c>
-      <c r="F80">
-        <v>1.1092064132297999E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F80" s="5">
+        <v>2.0167389331450999E-3</v>
       </c>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B81">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C81" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
-      <c r="F81">
-        <v>1.0083694665725499E-4</v>
+      <c r="F81" s="5">
+        <v>2.0167389331450999E-3</v>
       </c>
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.25">
@@ -5176,21 +5412,21 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D82" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E82" t="s">
-        <v>7</v>
-      </c>
-      <c r="F82">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F82" s="5">
+        <v>1.91590198648784E-3</v>
       </c>
     </row>
     <row r="83" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B83">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -5199,61 +5435,61 @@
         <v>6</v>
       </c>
       <c r="E83" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F83" s="5">
+        <v>1.91590198648784E-3</v>
       </c>
     </row>
     <row r="84" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B84">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C84" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E84" t="s">
         <v>9</v>
       </c>
-      <c r="F84">
-        <v>4.0334778662901998E-4</v>
+      <c r="F84" s="5">
+        <v>1.91590198648784E-3</v>
       </c>
     </row>
     <row r="85" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B85">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C85" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D85" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E85" t="s">
-        <v>10</v>
-      </c>
-      <c r="F85">
-        <v>1.00836946657255E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F85" s="5">
+        <v>1.81506503983059E-3</v>
       </c>
     </row>
     <row r="86" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B86">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C86" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D86" t="s">
         <v>7</v>
       </c>
       <c r="E86" t="s">
-        <v>8</v>
-      </c>
-      <c r="F86">
-        <v>3.0251083997176502E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F86" s="5">
+        <v>1.81506503983059E-3</v>
       </c>
     </row>
     <row r="87" spans="2:6" x14ac:dyDescent="0.25">
@@ -5261,152 +5497,152 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D87" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E87" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87">
-        <v>1.1092064132297999E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F87" s="5">
+        <v>1.7142280931733301E-3</v>
       </c>
     </row>
     <row r="88" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B88">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C88" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D88" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E88" t="s">
-        <v>10</v>
-      </c>
-      <c r="F88">
-        <v>1.1092064132297999E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F88" s="5">
+        <v>1.7142280931733301E-3</v>
       </c>
     </row>
     <row r="89" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B89">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C89" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D89" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89">
-        <v>8.0669557325804104E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F89" s="5">
+        <v>1.7142280931733301E-3</v>
       </c>
     </row>
     <row r="90" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B90">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
       </c>
       <c r="D90" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" t="s">
         <v>9</v>
       </c>
-      <c r="F90">
-        <v>8.0669557325804104E-4</v>
+      <c r="F90" s="5">
+        <v>1.7142280931733301E-3</v>
       </c>
     </row>
     <row r="91" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B91">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C91" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D91" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
       </c>
-      <c r="F91">
-        <v>5.0418473328627596E-4</v>
+      <c r="F91" s="5">
+        <v>1.6133911465160799E-3</v>
       </c>
     </row>
     <row r="92" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B92">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C92" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D92" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E92" t="s">
         <v>9</v>
       </c>
-      <c r="F92">
-        <v>2.0167389331450999E-4</v>
+      <c r="F92" s="5">
+        <v>1.6133911465160799E-3</v>
       </c>
     </row>
     <row r="93" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B93">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
       </c>
       <c r="D93" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E93" t="s">
         <v>10</v>
       </c>
-      <c r="F93">
-        <v>3.0251083997176502E-4</v>
+      <c r="F93" s="5">
+        <v>1.6133911465160799E-3</v>
       </c>
     </row>
     <row r="94" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B94">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C94" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D94" t="s">
         <v>7</v>
       </c>
       <c r="E94" t="s">
-        <v>9</v>
-      </c>
-      <c r="F94">
-        <v>1.0083694665725499E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F94" s="5">
+        <v>1.6133911465160799E-3</v>
       </c>
     </row>
     <row r="95" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B95">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C95" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D95" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
       </c>
-      <c r="F95">
-        <v>2.0167389331450999E-4</v>
+      <c r="F95" s="5">
+        <v>1.6133911465160799E-3</v>
       </c>
     </row>
     <row r="96" spans="2:6" x14ac:dyDescent="0.25">
@@ -5414,72 +5650,72 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D96" t="s">
         <v>6</v>
       </c>
       <c r="E96" t="s">
-        <v>7</v>
-      </c>
-      <c r="F96">
-        <v>2.0167389331450999E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F96" s="5">
+        <v>1.51255419985882E-3</v>
       </c>
     </row>
     <row r="97" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B97">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C97" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D97" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E97" t="s">
-        <v>8</v>
-      </c>
-      <c r="F97">
-        <v>1.7142280931733301E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F97" s="5">
+        <v>1.51255419985882E-3</v>
       </c>
     </row>
     <row r="98" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D98" t="s">
         <v>6</v>
       </c>
       <c r="E98" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98">
-        <v>2.72259755974589E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F98" s="5">
+        <v>1.41171725320157E-3</v>
       </c>
     </row>
     <row r="99" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D99" t="s">
         <v>6</v>
       </c>
       <c r="E99" t="s">
-        <v>10</v>
-      </c>
-      <c r="F99">
-        <v>1.6133911465160799E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F99" s="5">
+        <v>1.41171725320157E-3</v>
       </c>
     </row>
     <row r="100" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B100">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C100" t="s">
         <v>5</v>
@@ -5488,78 +5724,78 @@
         <v>7</v>
       </c>
       <c r="E100" t="s">
-        <v>7</v>
-      </c>
-      <c r="F100">
-        <v>7.0585862660078598E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F100" s="5">
+        <v>1.41171725320157E-3</v>
       </c>
     </row>
     <row r="101" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B101">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C101" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D101" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E101" t="s">
-        <v>8</v>
-      </c>
-      <c r="F101">
-        <v>2.3797519411112199E-2</v>
+        <v>9</v>
+      </c>
+      <c r="F101" s="5">
+        <v>1.41171725320157E-3</v>
       </c>
     </row>
     <row r="102" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C102" t="s">
         <v>5</v>
       </c>
       <c r="D102" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
         <v>9</v>
       </c>
-      <c r="F102">
-        <v>1.61339114651608E-2</v>
+      <c r="F102" s="5">
+        <v>1.3108803065443101E-3</v>
       </c>
     </row>
     <row r="103" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B103">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C103" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D103" t="s">
         <v>7</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
-      </c>
-      <c r="F103">
-        <v>5.6468690128062904E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F103" s="5">
+        <v>1.3108803065443101E-3</v>
       </c>
     </row>
     <row r="104" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B104">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C104" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D104" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E104" t="s">
-        <v>8</v>
-      </c>
-      <c r="F104">
-        <v>7.3610971059796301E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F104" s="5">
+        <v>1.2100433598870601E-3</v>
       </c>
     </row>
     <row r="105" spans="2:6" x14ac:dyDescent="0.25">
@@ -5567,58 +5803,58 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D105" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E105" t="s">
-        <v>9</v>
-      </c>
-      <c r="F105">
-        <v>8.5711404658666904E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F105" s="5">
+        <v>1.2100433598870601E-3</v>
       </c>
     </row>
     <row r="106" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B106">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C106" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D106" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
-      <c r="F106">
-        <v>6.1510537460925602E-3</v>
+      <c r="F106" s="5">
+        <v>1.2100433598870601E-3</v>
       </c>
     </row>
     <row r="107" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107" t="s">
         <v>5</v>
       </c>
       <c r="D107" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E107" t="s">
-        <v>9</v>
-      </c>
-      <c r="F107">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F107" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="108" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D108" t="s">
         <v>9</v>
@@ -5626,42 +5862,42 @@
       <c r="E108" t="s">
         <v>10</v>
       </c>
-      <c r="F108">
-        <v>2.6217606130886301E-3</v>
+      <c r="F108" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="109" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D109" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E109" t="s">
-        <v>10</v>
-      </c>
-      <c r="F109">
-        <v>4.0334778662901998E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F109" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="110" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B110">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D110" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E110" t="s">
-        <v>7</v>
-      </c>
-      <c r="F110">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F110" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="111" spans="2:6" x14ac:dyDescent="0.25">
@@ -5669,143 +5905,143 @@
         <v>4</v>
       </c>
       <c r="C111" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D111" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E111" t="s">
-        <v>8</v>
-      </c>
-      <c r="F111">
-        <v>2.2184128264596099E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F111" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="112" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B112">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D112" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E112" t="s">
-        <v>9</v>
-      </c>
-      <c r="F112">
-        <v>2.9242714530603999E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F112" s="5">
+        <v>1.1092064132297999E-3</v>
       </c>
     </row>
     <row r="113" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B113">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C113" t="s">
         <v>11</v>
       </c>
       <c r="D113" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113">
-        <v>3.73096702631844E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F113" s="5">
+        <v>1.00836946657255E-3</v>
       </c>
     </row>
     <row r="114" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C114" t="s">
         <v>11</v>
       </c>
       <c r="D114" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E114" t="s">
-        <v>8</v>
-      </c>
-      <c r="F114">
-        <v>9.9828577190682593E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F114" s="5">
+        <v>1.00836946657255E-3</v>
       </c>
     </row>
     <row r="115" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B115">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C115" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D115" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E115" t="s">
-        <v>9</v>
-      </c>
-      <c r="F115">
-        <v>1.5932237571846301E-2</v>
+        <v>10</v>
+      </c>
+      <c r="F115" s="5">
+        <v>1.00836946657255E-3</v>
       </c>
     </row>
     <row r="116" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B116">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C116" t="s">
         <v>11</v>
       </c>
       <c r="D116" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116">
-        <v>1.52263789452455E-2</v>
+        <v>9</v>
+      </c>
+      <c r="F116" s="5">
+        <v>1.00836946657255E-3</v>
       </c>
     </row>
     <row r="117" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B117">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C117" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D117" t="s">
         <v>8</v>
       </c>
       <c r="E117" t="s">
-        <v>8</v>
-      </c>
-      <c r="F117">
-        <v>4.0334778662901999E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F117" s="5">
+        <v>1.00836946657255E-3</v>
       </c>
     </row>
     <row r="118" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B118">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C118" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D118" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E118" t="s">
-        <v>9</v>
-      </c>
-      <c r="F118">
-        <v>7.2602601593223697E-3</v>
+        <v>6</v>
+      </c>
+      <c r="F118" s="5">
+        <v>9.0753251991529697E-4</v>
       </c>
     </row>
     <row r="119" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B119">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C119" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D119" t="s">
         <v>8</v>
@@ -5813,76 +6049,76 @@
       <c r="E119" t="s">
         <v>10</v>
       </c>
-      <c r="F119">
-        <v>1.00836946657255E-2</v>
+      <c r="F119" s="5">
+        <v>9.0753251991529697E-4</v>
       </c>
     </row>
     <row r="120" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B120">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C120" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D120" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E120" t="s">
         <v>9</v>
       </c>
-      <c r="F120">
-        <v>1.0083694665725499E-4</v>
+      <c r="F120" s="5">
+        <v>9.0753251991529697E-4</v>
       </c>
     </row>
     <row r="121" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B121">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C121" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D121" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E121" t="s">
         <v>10</v>
       </c>
-      <c r="F121">
-        <v>1.7142280931733301E-3</v>
+      <c r="F121" s="5">
+        <v>9.0753251991529697E-4</v>
       </c>
     </row>
     <row r="122" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B122">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C122" t="s">
         <v>12</v>
       </c>
       <c r="D122" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E122" t="s">
-        <v>7</v>
-      </c>
-      <c r="F122">
-        <v>1.0083694665725499E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F122" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="123" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B123">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C123" t="s">
         <v>12</v>
       </c>
       <c r="D123" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E123" t="s">
-        <v>8</v>
-      </c>
-      <c r="F123">
-        <v>1.51255419985882E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F123" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="124" spans="2:6" x14ac:dyDescent="0.25">
@@ -5898,178 +6134,178 @@
       <c r="E124" t="s">
         <v>9</v>
       </c>
-      <c r="F124">
+      <c r="F124" s="5">
         <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="125" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B125">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C125" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D125" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125">
-        <v>1.91590198648784E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F125" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="126" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B126">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C126" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D126" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E126" t="s">
-        <v>8</v>
-      </c>
-      <c r="F126">
-        <v>1.2100433598870601E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F126" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="127" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B127">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C127" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E127" t="s">
         <v>9</v>
       </c>
-      <c r="F127">
-        <v>1.7142280931733301E-3</v>
+      <c r="F127" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="128" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B128">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C128" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D128" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
       </c>
-      <c r="F128">
-        <v>5.1426842795200102E-3</v>
+      <c r="F128" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="129" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B129">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C129" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D129" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E129" t="s">
-        <v>8</v>
-      </c>
-      <c r="F129">
-        <v>2.0167389331450999E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F129" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="130" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B130">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C130" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D130" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E130" t="s">
         <v>9</v>
       </c>
-      <c r="F130">
-        <v>1.1092064132297999E-3</v>
+      <c r="F130" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="131" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B131">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D131" t="s">
         <v>8</v>
       </c>
       <c r="E131" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131">
-        <v>2.0167389331450999E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F131" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="132" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B132">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C132" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D132" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E132" t="s">
         <v>10</v>
       </c>
-      <c r="F132">
-        <v>3.0251083997176502E-4</v>
+      <c r="F132" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="133" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B133">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C133" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D133" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E133" t="s">
         <v>10</v>
       </c>
-      <c r="F133">
-        <v>1.0083694665725499E-4</v>
+      <c r="F133" s="5">
+        <v>8.0669557325804104E-4</v>
       </c>
     </row>
     <row r="134" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B134">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C134" t="s">
         <v>13</v>
       </c>
       <c r="D134" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E134" t="s">
-        <v>9</v>
-      </c>
-      <c r="F134">
-        <v>6.0502167994353102E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F134" s="5">
+        <v>7.0585862660078598E-4</v>
       </c>
     </row>
     <row r="135" spans="2:6" x14ac:dyDescent="0.25">
@@ -6077,92 +6313,92 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D135" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E135" t="s">
-        <v>10</v>
-      </c>
-      <c r="F135">
-        <v>2.0167389331450999E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F135" s="5">
+        <v>7.0585862660078598E-4</v>
       </c>
     </row>
     <row r="136" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B136">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C136" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D136" t="s">
         <v>7</v>
       </c>
       <c r="E136" t="s">
-        <v>9</v>
-      </c>
-      <c r="F136">
-        <v>3.0251083997176502E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F136" s="5">
+        <v>7.0585862660078598E-4</v>
       </c>
     </row>
     <row r="137" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B137">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C137" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D137" t="s">
         <v>7</v>
       </c>
       <c r="E137" t="s">
-        <v>10</v>
-      </c>
-      <c r="F137">
-        <v>5.0418473328627596E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F137" s="5">
+        <v>7.0585862660078598E-4</v>
       </c>
     </row>
     <row r="138" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B138">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C138" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D138" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E138" t="s">
-        <v>9</v>
-      </c>
-      <c r="F138">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F138" s="5">
+        <v>7.0585862660078598E-4</v>
       </c>
     </row>
     <row r="139" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B139">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C139" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D139" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E139" t="s">
-        <v>10</v>
-      </c>
-      <c r="F139">
-        <v>5.0418473328627596E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F139" s="5">
+        <v>6.0502167994353102E-4</v>
       </c>
     </row>
     <row r="140" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B140">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D140" t="s">
         <v>6</v>
@@ -6170,144 +6406,144 @@
       <c r="E140" t="s">
         <v>9</v>
       </c>
-      <c r="F140">
-        <v>1.0083694665725499E-4</v>
+      <c r="F140" s="5">
+        <v>6.0502167994353102E-4</v>
       </c>
     </row>
     <row r="141" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B141">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C141" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D141" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E141" t="s">
         <v>10</v>
       </c>
-      <c r="F141">
-        <v>1.0083694665725499E-4</v>
+      <c r="F141" s="5">
+        <v>6.0502167994353102E-4</v>
       </c>
     </row>
     <row r="142" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B142">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C142" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D142" t="s">
         <v>7</v>
       </c>
       <c r="E142" t="s">
-        <v>8</v>
-      </c>
-      <c r="F142">
-        <v>3.9326409196329499E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F142" s="5">
+        <v>6.0502167994353102E-4</v>
       </c>
     </row>
     <row r="143" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B143">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C143" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D143" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E143" t="s">
         <v>9</v>
       </c>
-      <c r="F143">
-        <v>2.3192497731168698E-3</v>
+      <c r="F143" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="144" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B144">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C144" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D144" t="s">
         <v>7</v>
       </c>
       <c r="E144" t="s">
-        <v>10</v>
-      </c>
-      <c r="F144">
-        <v>1.41171725320157E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F144" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="145" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B145">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C145" t="s">
         <v>5</v>
       </c>
       <c r="D145" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E145" t="s">
-        <v>8</v>
-      </c>
-      <c r="F145">
-        <v>8.0669557325804104E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F145" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="146" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B146">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C146" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D146" t="s">
         <v>8</v>
       </c>
       <c r="E146" t="s">
-        <v>9</v>
-      </c>
-      <c r="F146">
-        <v>1.6133911465160799E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F146" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="147" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B147">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D147" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E147" t="s">
         <v>10</v>
       </c>
-      <c r="F147">
-        <v>8.0669557325804104E-4</v>
+      <c r="F147" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="148" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D148" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E148" t="s">
         <v>10</v>
       </c>
-      <c r="F148">
-        <v>4.0334778662901998E-4</v>
+      <c r="F148" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="149" spans="2:6" x14ac:dyDescent="0.25">
@@ -6318,52 +6554,52 @@
         <v>11</v>
       </c>
       <c r="D149" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E149" t="s">
         <v>8</v>
       </c>
-      <c r="F149">
-        <v>3.0251083997176502E-4</v>
+      <c r="F149" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="150" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B150">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C150" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D150" t="s">
         <v>6</v>
       </c>
       <c r="E150" t="s">
-        <v>9</v>
-      </c>
-      <c r="F150">
-        <v>1.00836946657255E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F150" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="151" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B151">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D151" t="s">
         <v>6</v>
       </c>
       <c r="E151" t="s">
-        <v>10</v>
-      </c>
-      <c r="F151">
-        <v>4.0334778662901998E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F151" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="152" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B152">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C152" t="s">
         <v>11</v>
@@ -6372,112 +6608,112 @@
         <v>7</v>
       </c>
       <c r="E152" t="s">
-        <v>7</v>
-      </c>
-      <c r="F152">
-        <v>3.0251083997176502E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F152" s="5">
+        <v>5.0418473328627596E-4</v>
       </c>
     </row>
     <row r="153" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B153">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C153" t="s">
         <v>11</v>
       </c>
       <c r="D153" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E153" t="s">
-        <v>8</v>
-      </c>
-      <c r="F153">
-        <v>3.2267822930321598E-3</v>
+        <v>7</v>
+      </c>
+      <c r="F153" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="154" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B154">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C154" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D154" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E154" t="s">
-        <v>9</v>
-      </c>
-      <c r="F154">
-        <v>5.4451951194917801E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F154" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="155" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B155">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C155" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D155" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E155" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155">
-        <v>3.5292931330039301E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F155" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="156" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B156">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C156" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D156" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E156" t="s">
-        <v>8</v>
-      </c>
-      <c r="F156">
-        <v>5.0418473328627596E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F156" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="157" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B157">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C157" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D157" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E157" t="s">
         <v>9</v>
       </c>
-      <c r="F157">
-        <v>1.41171725320157E-3</v>
+      <c r="F157" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="158" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B158">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C158" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D158" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
       </c>
-      <c r="F158">
-        <v>3.2267822930321598E-3</v>
+      <c r="F158" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="159" spans="2:6" x14ac:dyDescent="0.25">
@@ -6485,7 +6721,7 @@
         <v>5</v>
       </c>
       <c r="C159" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D159" t="s">
         <v>9</v>
@@ -6493,8 +6729,8 @@
       <c r="E159" t="s">
         <v>10</v>
       </c>
-      <c r="F159">
-        <v>2.0167389331450999E-4</v>
+      <c r="F159" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="160" spans="2:6" x14ac:dyDescent="0.25">
@@ -6502,16 +6738,16 @@
         <v>5</v>
       </c>
       <c r="C160" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D160" t="s">
         <v>6</v>
       </c>
       <c r="E160" t="s">
-        <v>8</v>
-      </c>
-      <c r="F160">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F160" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="161" spans="2:6" x14ac:dyDescent="0.25">
@@ -6527,254 +6763,254 @@
       <c r="E161" t="s">
         <v>9</v>
       </c>
-      <c r="F161">
+      <c r="F161" s="5">
         <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="162" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B162">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C162" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D162" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E162" t="s">
-        <v>10</v>
-      </c>
-      <c r="F162">
-        <v>2.0167389331450999E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F162" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="163" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B163">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C163" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D163" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E163" t="s">
         <v>8</v>
       </c>
-      <c r="F163">
-        <v>3.0251083997176502E-4</v>
+      <c r="F163" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="164" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B164">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C164" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D164" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164">
-        <v>9.0753251991529697E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F164" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="165" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B165">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C165" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D165" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E165" t="s">
         <v>10</v>
       </c>
-      <c r="F165">
-        <v>1.6133911465160799E-3</v>
+      <c r="F165" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="166" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B166">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C166" t="s">
         <v>12</v>
       </c>
       <c r="D166" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E166" t="s">
         <v>9</v>
       </c>
-      <c r="F166">
-        <v>3.0251083997176502E-4</v>
+      <c r="F166" s="5">
+        <v>4.0334778662901998E-4</v>
       </c>
     </row>
     <row r="167" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B167">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C167" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D167" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E167" t="s">
-        <v>10</v>
-      </c>
-      <c r="F167">
-        <v>1.00836946657255E-3</v>
+        <v>6</v>
+      </c>
+      <c r="F167" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="168" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B168">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C168" t="s">
         <v>13</v>
       </c>
       <c r="D168" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E168" t="s">
-        <v>9</v>
-      </c>
-      <c r="F168">
-        <v>1.0083694665725499E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F168" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="169" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B169">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C169" t="s">
         <v>13</v>
       </c>
       <c r="D169" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E169" t="s">
         <v>10</v>
       </c>
-      <c r="F169">
-        <v>2.0167389331450999E-4</v>
+      <c r="F169" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="170" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B170">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C170" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D170" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E170" t="s">
         <v>8</v>
       </c>
-      <c r="F170">
-        <v>1.0083694665725499E-4</v>
+      <c r="F170" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="171" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B171">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C171" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D171" t="s">
         <v>7</v>
       </c>
       <c r="E171" t="s">
-        <v>10</v>
-      </c>
-      <c r="F171">
-        <v>2.0167389331450999E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F171" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="172" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B172">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C172" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D172" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
         <v>10</v>
       </c>
-      <c r="F172">
-        <v>1.0083694665725499E-4</v>
+      <c r="F172" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="173" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B173">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C173" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D173" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E173" t="s">
-        <v>8</v>
-      </c>
-      <c r="F173">
-        <v>5.0418473328627596E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F173" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="174" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B174">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C174" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D174" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E174" t="s">
         <v>9</v>
       </c>
-      <c r="F174">
+      <c r="F174" s="5">
         <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="175" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B175">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C175" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D175" t="s">
         <v>6</v>
       </c>
       <c r="E175" t="s">
-        <v>10</v>
-      </c>
-      <c r="F175">
+        <v>8</v>
+      </c>
+      <c r="F175" s="5">
         <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="176" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B176">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C176" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D176" t="s">
         <v>7</v>
@@ -6782,16 +7018,16 @@
       <c r="E176" t="s">
         <v>7</v>
       </c>
-      <c r="F176">
-        <v>2.0167389331450999E-4</v>
+      <c r="F176" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="177" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B177">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C177" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D177" t="s">
         <v>7</v>
@@ -6799,25 +7035,25 @@
       <c r="E177" t="s">
         <v>8</v>
       </c>
-      <c r="F177">
-        <v>3.2267822930321598E-3</v>
+      <c r="F177" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="178" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B178">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C178" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D178" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E178" t="s">
         <v>9</v>
       </c>
-      <c r="F178">
-        <v>5.54603206614903E-3</v>
+      <c r="F178" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="179" spans="2:6" x14ac:dyDescent="0.25">
@@ -6828,13 +7064,13 @@
         <v>5</v>
       </c>
       <c r="D179" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E179" t="s">
-        <v>10</v>
-      </c>
-      <c r="F179">
-        <v>2.9242714530603999E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F179" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="180" spans="2:6" x14ac:dyDescent="0.25">
@@ -6845,13 +7081,13 @@
         <v>5</v>
       </c>
       <c r="D180" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E180" t="s">
-        <v>8</v>
-      </c>
-      <c r="F180">
-        <v>4.0334778662901998E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F180" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="181" spans="2:6" x14ac:dyDescent="0.25">
@@ -6859,16 +7095,16 @@
         <v>6</v>
       </c>
       <c r="C181" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D181" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E181" t="s">
-        <v>9</v>
-      </c>
-      <c r="F181">
-        <v>8.0669557325804104E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F181" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="182" spans="2:6" x14ac:dyDescent="0.25">
@@ -6876,16 +7112,16 @@
         <v>6</v>
       </c>
       <c r="C182" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E182" t="s">
         <v>10</v>
       </c>
-      <c r="F182">
-        <v>8.0669557325804104E-4</v>
+      <c r="F182" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="183" spans="2:6" x14ac:dyDescent="0.25">
@@ -6893,16 +7129,16 @@
         <v>6</v>
       </c>
       <c r="C183" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D183" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E183" t="s">
-        <v>9</v>
-      </c>
-      <c r="F183">
-        <v>1.0083694665725499E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F183" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="184" spans="2:6" x14ac:dyDescent="0.25">
@@ -6910,15 +7146,15 @@
         <v>6</v>
       </c>
       <c r="C184" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D184" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E184" t="s">
-        <v>8</v>
-      </c>
-      <c r="F184">
+        <v>10</v>
+      </c>
+      <c r="F184" s="5">
         <v>3.0251083997176502E-4</v>
       </c>
     </row>
@@ -6927,41 +7163,41 @@
         <v>6</v>
       </c>
       <c r="C185" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D185" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E185" t="s">
-        <v>9</v>
-      </c>
-      <c r="F185">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F185" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="186" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B186">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C186" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D186" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E186" t="s">
         <v>10</v>
       </c>
-      <c r="F186">
-        <v>1.2100433598870601E-3</v>
+      <c r="F186" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="187" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B187">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C187" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D187" t="s">
         <v>7</v>
@@ -6969,16 +7205,16 @@
       <c r="E187" t="s">
         <v>8</v>
       </c>
-      <c r="F187">
-        <v>4.1343148129474603E-3</v>
+      <c r="F187" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="188" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B188">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C188" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D188" t="s">
         <v>7</v>
@@ -6986,13 +7222,13 @@
       <c r="E188" t="s">
         <v>9</v>
       </c>
-      <c r="F188">
-        <v>4.4368256529192197E-3</v>
+      <c r="F188" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="189" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B189">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -7003,246 +7239,246 @@
       <c r="E189" t="s">
         <v>10</v>
       </c>
-      <c r="F189">
-        <v>6.1510537460925602E-3</v>
+      <c r="F189" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="190" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B190">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C190" t="s">
         <v>11</v>
       </c>
       <c r="D190" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E190" t="s">
-        <v>8</v>
-      </c>
-      <c r="F190">
-        <v>4.0334778662901998E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F190" s="5">
+        <v>3.0251083997176502E-4</v>
       </c>
     </row>
     <row r="191" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B191">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C191" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D191" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E191" t="s">
         <v>9</v>
       </c>
-      <c r="F191">
-        <v>1.81506503983059E-3</v>
+      <c r="F191" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="192" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B192">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C192" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D192" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E192" t="s">
-        <v>10</v>
-      </c>
-      <c r="F192">
-        <v>2.3192497731168698E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F192" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="193" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B193">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C193" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D193" t="s">
         <v>9</v>
       </c>
       <c r="E193" t="s">
-        <v>10</v>
-      </c>
-      <c r="F193">
-        <v>3.0251083997176502E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F193" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="194" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B194">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C194" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D194" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E194" t="s">
-        <v>8</v>
-      </c>
-      <c r="F194">
-        <v>3.0251083997176502E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F194" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="195" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B195">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C195" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D195" t="s">
         <v>6</v>
       </c>
       <c r="E195" t="s">
-        <v>9</v>
-      </c>
-      <c r="F195">
-        <v>5.0418473328627596E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F195" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="196" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B196">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C196" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D196" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E196" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196">
-        <v>1.0083694665725499E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F196" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="197" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B197">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C197" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D197" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E197" t="s">
-        <v>8</v>
-      </c>
-      <c r="F197">
-        <v>1.0083694665725499E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F197" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="198" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B198">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C198" t="s">
         <v>12</v>
       </c>
       <c r="D198" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E198" t="s">
-        <v>9</v>
-      </c>
-      <c r="F198">
-        <v>1.51255419985882E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F198" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="199" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B199">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C199" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D199" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E199" t="s">
         <v>10</v>
       </c>
-      <c r="F199">
-        <v>3.3276192396894202E-3</v>
+      <c r="F199" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="200" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B200">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C200" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D200" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E200" t="s">
-        <v>8</v>
-      </c>
-      <c r="F200">
+        <v>10</v>
+      </c>
+      <c r="F200" s="5">
         <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="201" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B201">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C201" t="s">
         <v>12</v>
       </c>
       <c r="D201" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E201" t="s">
-        <v>9</v>
-      </c>
-      <c r="F201">
+        <v>10</v>
+      </c>
+      <c r="F201" s="5">
         <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="202" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B202">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C202" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D202" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E202" t="s">
         <v>10</v>
       </c>
-      <c r="F202">
-        <v>6.0502167994353102E-4</v>
+      <c r="F202" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="203" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B203">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C203" t="s">
         <v>13</v>
       </c>
       <c r="D203" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E203" t="s">
-        <v>9</v>
-      </c>
-      <c r="F203">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F203" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="204" spans="2:6" x14ac:dyDescent="0.25">
@@ -7250,16 +7486,16 @@
         <v>6</v>
       </c>
       <c r="C204" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D204" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E204" t="s">
-        <v>10</v>
-      </c>
-      <c r="F204">
-        <v>1.0083694665725499E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F204" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="205" spans="2:6" x14ac:dyDescent="0.25">
@@ -7267,16 +7503,16 @@
         <v>6</v>
       </c>
       <c r="C205" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D205" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E205" t="s">
         <v>8</v>
       </c>
-      <c r="F205">
-        <v>1.0083694665725499E-4</v>
+      <c r="F205" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="206" spans="2:6" x14ac:dyDescent="0.25">
@@ -7284,15 +7520,15 @@
         <v>6</v>
       </c>
       <c r="C206" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D206" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E206" t="s">
         <v>9</v>
       </c>
-      <c r="F206">
+      <c r="F206" s="5">
         <v>2.0167389331450999E-4</v>
       </c>
     </row>
@@ -7307,18 +7543,18 @@
         <v>7</v>
       </c>
       <c r="E207" t="s">
-        <v>10</v>
-      </c>
-      <c r="F207">
-        <v>3.0251083997176502E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F207" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="208" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B208">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C208" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
         <v>8</v>
@@ -7326,16 +7562,16 @@
       <c r="E208" t="s">
         <v>9</v>
       </c>
-      <c r="F208">
-        <v>1.0083694665725499E-4</v>
+      <c r="F208" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="209" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B209">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C209" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D209" t="s">
         <v>8</v>
@@ -7343,8 +7579,8 @@
       <c r="E209" t="s">
         <v>10</v>
       </c>
-      <c r="F209">
-        <v>3.0251083997176502E-4</v>
+      <c r="F209" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="210" spans="2:6" x14ac:dyDescent="0.25">
@@ -7352,21 +7588,21 @@
         <v>7</v>
       </c>
       <c r="C210" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D210" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E210" t="s">
-        <v>9</v>
-      </c>
-      <c r="F210">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F210" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="211" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B211">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C211" t="s">
         <v>5</v>
@@ -7377,13 +7613,13 @@
       <c r="E211" t="s">
         <v>8</v>
       </c>
-      <c r="F211">
-        <v>1.1092064132297999E-3</v>
+      <c r="F211" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="212" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B212">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C212" t="s">
         <v>5</v>
@@ -7394,13 +7630,13 @@
       <c r="E212" t="s">
         <v>9</v>
       </c>
-      <c r="F212">
-        <v>8.0669557325804104E-4</v>
+      <c r="F212" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="213" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B213">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C213" t="s">
         <v>5</v>
@@ -7411,67 +7647,67 @@
       <c r="E213" t="s">
         <v>10</v>
       </c>
-      <c r="F213">
-        <v>3.0251083997176502E-4</v>
+      <c r="F213" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="214" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B214">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C214" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D214" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E214" t="s">
-        <v>9</v>
-      </c>
-      <c r="F214">
+        <v>10</v>
+      </c>
+      <c r="F214" s="5">
         <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="215" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B215">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C215" t="s">
         <v>5</v>
       </c>
       <c r="D215" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E215" t="s">
-        <v>10</v>
-      </c>
-      <c r="F215">
+        <v>9</v>
+      </c>
+      <c r="F215" s="5">
         <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="216" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B216">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C216" t="s">
         <v>11</v>
       </c>
       <c r="D216" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E216" t="s">
-        <v>9</v>
-      </c>
-      <c r="F216">
-        <v>8.0669557325804104E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F216" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="217" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B217">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C217" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D217" t="s">
         <v>6</v>
@@ -7479,13 +7715,13 @@
       <c r="E217" t="s">
         <v>10</v>
       </c>
-      <c r="F217">
-        <v>4.0334778662901998E-4</v>
+      <c r="F217" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="218" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B218">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C218" t="s">
         <v>11</v>
@@ -7494,32 +7730,32 @@
         <v>7</v>
       </c>
       <c r="E218" t="s">
-        <v>8</v>
-      </c>
-      <c r="F218">
-        <v>1.6133911465160799E-3</v>
+        <v>9</v>
+      </c>
+      <c r="F218" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="219" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B219">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C219" t="s">
         <v>11</v>
       </c>
       <c r="D219" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E219" t="s">
         <v>9</v>
       </c>
-      <c r="F219">
-        <v>3.1259453463749099E-3</v>
+      <c r="F219" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="220" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B220">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C220" t="s">
         <v>11</v>
@@ -7528,256 +7764,256 @@
         <v>7</v>
       </c>
       <c r="E220" t="s">
-        <v>10</v>
-      </c>
-      <c r="F220">
-        <v>1.81506503983059E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F220" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="221" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B221">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C221" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D221" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E221" t="s">
-        <v>8</v>
-      </c>
-      <c r="F221">
-        <v>1.0083694665725499E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F221" s="5">
+        <v>2.0167389331450999E-4</v>
       </c>
     </row>
     <row r="222" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B222">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C222" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D222" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E222" t="s">
-        <v>9</v>
-      </c>
-      <c r="F222">
-        <v>8.0669557325804104E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F222" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="223" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B223">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C223" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D223" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E223" t="s">
-        <v>10</v>
-      </c>
-      <c r="F223">
-        <v>4.0334778662901998E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F223" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="224" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B224">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C224" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D224" t="s">
         <v>6</v>
       </c>
       <c r="E224" t="s">
-        <v>10</v>
-      </c>
-      <c r="F224">
+        <v>6</v>
+      </c>
+      <c r="F224" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="225" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B225">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C225" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E225" t="s">
         <v>8</v>
       </c>
-      <c r="F225">
-        <v>3.0251083997176502E-4</v>
+      <c r="F225" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="226" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B226">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="C226" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D226" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E226" t="s">
-        <v>9</v>
-      </c>
-      <c r="F226">
-        <v>1.3108803065443101E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F226" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="227" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B227">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C227" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D227" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E227" t="s">
-        <v>10</v>
-      </c>
-      <c r="F227">
-        <v>9.0753251991529697E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F227" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="228" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B228">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C228" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D228" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E228" t="s">
-        <v>10</v>
-      </c>
-      <c r="F228">
-        <v>2.0167389331450999E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F228" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="229" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B229">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C229" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D229" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E229" t="s">
-        <v>9</v>
-      </c>
-      <c r="F229">
+        <v>10</v>
+      </c>
+      <c r="F229" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="230" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B230">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C230" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D230" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E230" t="s">
-        <v>10</v>
-      </c>
-      <c r="F230">
+        <v>7</v>
+      </c>
+      <c r="F230" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="231" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B231">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C231" t="s">
         <v>13</v>
       </c>
       <c r="D231" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E231" t="s">
-        <v>10</v>
-      </c>
-      <c r="F231">
+        <v>9</v>
+      </c>
+      <c r="F231" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="232" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B232">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C232" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D232" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E232" t="s">
-        <v>8</v>
-      </c>
-      <c r="F232">
-        <v>2.0167389331450999E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F232" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="233" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B233">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C233" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D233" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E233" t="s">
-        <v>9</v>
-      </c>
-      <c r="F233">
-        <v>2.0167389331450999E-4</v>
+        <v>7</v>
+      </c>
+      <c r="F233" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="234" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B234">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C234" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D234" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
       </c>
-      <c r="F234">
-        <v>2.0167389331450999E-4</v>
+      <c r="F234" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="235" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B235">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C235" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D235" t="s">
         <v>8</v>
@@ -7785,441 +8021,441 @@
       <c r="E235" t="s">
         <v>9</v>
       </c>
-      <c r="F235">
+      <c r="F235" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="236" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B236">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C236" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D236" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E236" t="s">
-        <v>8</v>
-      </c>
-      <c r="F236">
-        <v>7.0585862660078598E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F236" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="237" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B237">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C237" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D237" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E237" t="s">
-        <v>9</v>
-      </c>
-      <c r="F237">
-        <v>1.91590198648784E-3</v>
+        <v>10</v>
+      </c>
+      <c r="F237" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="238" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B238">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C238" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D238" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E238" t="s">
-        <v>10</v>
-      </c>
-      <c r="F238">
-        <v>1.6133911465160799E-3</v>
+        <v>8</v>
+      </c>
+      <c r="F238" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="239" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B239">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C239" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D239" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E239" t="s">
         <v>9</v>
       </c>
-      <c r="F239">
+      <c r="F239" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="240" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B240">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C240" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D240" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E240" t="s">
-        <v>10</v>
-      </c>
-      <c r="F240">
-        <v>8.0669557325804104E-4</v>
+        <v>8</v>
+      </c>
+      <c r="F240" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="241" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B241">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C241" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D241" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E241" t="s">
-        <v>8</v>
-      </c>
-      <c r="F241">
+        <v>10</v>
+      </c>
+      <c r="F241" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="242" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B242">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C242" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D242" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
         <v>9</v>
       </c>
-      <c r="F242">
-        <v>7.0585862660078598E-4</v>
+      <c r="F242" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="243" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B243">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C243" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D243" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E243" t="s">
-        <v>10</v>
-      </c>
-      <c r="F243">
-        <v>7.0585862660078598E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F243" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="244" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B244">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C244" t="s">
         <v>12</v>
       </c>
       <c r="D244" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E244" t="s">
         <v>10</v>
       </c>
-      <c r="F244">
+      <c r="F244" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="245" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B245">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C245" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D245" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E245" t="s">
-        <v>9</v>
-      </c>
-      <c r="F245">
+        <v>8</v>
+      </c>
+      <c r="F245" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="246" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B246">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C246" t="s">
         <v>13</v>
       </c>
       <c r="D246" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E246" t="s">
         <v>9</v>
       </c>
-      <c r="F246">
+      <c r="F246" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="247" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B247">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C247" t="s">
         <v>13</v>
       </c>
       <c r="D247" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E247" t="s">
         <v>10</v>
       </c>
-      <c r="F247">
-        <v>2.0167389331450999E-4</v>
+      <c r="F247" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="248" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B248">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C248" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D248" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E248" t="s">
-        <v>10</v>
-      </c>
-      <c r="F248">
+        <v>8</v>
+      </c>
+      <c r="F248" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="249" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B249">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C249" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D249" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E249" t="s">
         <v>9</v>
       </c>
-      <c r="F249">
-        <v>2.0167389331450999E-4</v>
+      <c r="F249" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="250" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B250">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C250" t="s">
         <v>5</v>
       </c>
       <c r="D250" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E250" t="s">
-        <v>10</v>
-      </c>
-      <c r="F250">
+        <v>9</v>
+      </c>
+      <c r="F250" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="251" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B251">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C251" t="s">
         <v>11</v>
       </c>
       <c r="D251" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E251" t="s">
         <v>8</v>
       </c>
-      <c r="F251">
-        <v>2.0167389331450999E-4</v>
+      <c r="F251" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="252" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B252">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C252" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D252" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E252" t="s">
-        <v>9</v>
-      </c>
-      <c r="F252">
-        <v>5.0418473328627596E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F252" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="253" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B253">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C253" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D253" t="s">
         <v>7</v>
       </c>
       <c r="E253" t="s">
-        <v>10</v>
-      </c>
-      <c r="F253">
-        <v>6.0502167994353102E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F253" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="254" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B254">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C254" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D254" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E254" t="s">
-        <v>9</v>
-      </c>
-      <c r="F254">
+        <v>10</v>
+      </c>
+      <c r="F254" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="255" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B255">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C255" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D255" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E255" t="s">
         <v>10</v>
       </c>
-      <c r="F255">
-        <v>2.0167389331450999E-4</v>
+      <c r="F255" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="256" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B256">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C256" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D256" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E256" t="s">
         <v>9</v>
       </c>
-      <c r="F256">
-        <v>3.0251083997176502E-4</v>
+      <c r="F256" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="257" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B257">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C257" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D257" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E257" t="s">
-        <v>10</v>
-      </c>
-      <c r="F257">
+        <v>9</v>
+      </c>
+      <c r="F257" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="258" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B258">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C258" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D258" t="s">
         <v>7</v>
       </c>
       <c r="E258" t="s">
-        <v>10</v>
-      </c>
-      <c r="F258">
+        <v>8</v>
+      </c>
+      <c r="F258" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="259" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B259">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C259" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D259" t="s">
         <v>8</v>
       </c>
       <c r="E259" t="s">
-        <v>9</v>
-      </c>
-      <c r="F259">
+        <v>10</v>
+      </c>
+      <c r="F259" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="260" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B260">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C260" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D260" t="s">
         <v>6</v>
       </c>
       <c r="E260" t="s">
-        <v>10</v>
-      </c>
-      <c r="F260">
+        <v>9</v>
+      </c>
+      <c r="F260" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="261" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B261">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C261" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D261" t="s">
         <v>7</v>
@@ -8227,109 +8463,109 @@
       <c r="E261" t="s">
         <v>9</v>
       </c>
-      <c r="F261">
+      <c r="F261" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="262" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B262">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C262" t="s">
         <v>5</v>
       </c>
       <c r="D262" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E262" t="s">
         <v>10</v>
       </c>
-      <c r="F262">
+      <c r="F262" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="263" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B263">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C263" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D263" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E263" t="s">
-        <v>9</v>
-      </c>
-      <c r="F263">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F263" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="264" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B264">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C264" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D264" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E264" t="s">
-        <v>10</v>
-      </c>
-      <c r="F264">
-        <v>8.0669557325804104E-4</v>
+        <v>9</v>
+      </c>
+      <c r="F264" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="265" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B265">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C265" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D265" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E265" t="s">
-        <v>9</v>
-      </c>
-      <c r="F265">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F265" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="266" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B266">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C266" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D266" t="s">
         <v>7</v>
       </c>
       <c r="E266" t="s">
-        <v>9</v>
-      </c>
-      <c r="F266">
-        <v>4.0334778662901998E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F266" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="267" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B267">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C267" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D267" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E267" t="s">
-        <v>10</v>
-      </c>
-      <c r="F267">
+        <v>9</v>
+      </c>
+      <c r="F267" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8338,83 +8574,83 @@
         <v>10</v>
       </c>
       <c r="C268" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D268" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E268" t="s">
         <v>10</v>
       </c>
-      <c r="F268">
+      <c r="F268" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="269" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B269">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C269" t="s">
         <v>5</v>
       </c>
       <c r="D269" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E269" t="s">
-        <v>10</v>
-      </c>
-      <c r="F269">
+        <v>9</v>
+      </c>
+      <c r="F269" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="270" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B270">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C270" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D270" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E270" t="s">
         <v>10</v>
       </c>
-      <c r="F270">
+      <c r="F270" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="271" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B271">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C271" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D271" t="s">
         <v>7</v>
       </c>
       <c r="E271" t="s">
-        <v>8</v>
-      </c>
-      <c r="F271">
-        <v>2.0167389331450999E-4</v>
+        <v>10</v>
+      </c>
+      <c r="F271" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="272" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B272">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C272" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D272" t="s">
         <v>7</v>
       </c>
       <c r="E272" t="s">
-        <v>9</v>
-      </c>
-      <c r="F272">
+        <v>10</v>
+      </c>
+      <c r="F272" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8423,16 +8659,16 @@
         <v>11</v>
       </c>
       <c r="C273" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D273" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E273" t="s">
         <v>10</v>
       </c>
-      <c r="F273">
-        <v>3.0251083997176502E-4</v>
+      <c r="F273" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="274" spans="2:6" x14ac:dyDescent="0.25">
@@ -8440,15 +8676,15 @@
         <v>11</v>
       </c>
       <c r="C274" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D274" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E274" t="s">
-        <v>9</v>
-      </c>
-      <c r="F274">
+        <v>10</v>
+      </c>
+      <c r="F274" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8457,15 +8693,15 @@
         <v>11</v>
       </c>
       <c r="C275" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D275" t="s">
         <v>7</v>
       </c>
       <c r="E275" t="s">
-        <v>10</v>
-      </c>
-      <c r="F275">
+        <v>9</v>
+      </c>
+      <c r="F275" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8474,7 +8710,7 @@
         <v>11</v>
       </c>
       <c r="C276" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D276" t="s">
         <v>7</v>
@@ -8482,41 +8718,41 @@
       <c r="E276" t="s">
         <v>9</v>
       </c>
-      <c r="F276">
+      <c r="F276" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="277" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B277">
+        <v>11</v>
+      </c>
+      <c r="C277" t="s">
         <v>12</v>
       </c>
-      <c r="C277" t="s">
-        <v>5</v>
-      </c>
       <c r="D277" t="s">
         <v>7</v>
       </c>
       <c r="E277" t="s">
         <v>10</v>
       </c>
-      <c r="F277">
+      <c r="F277" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="278" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B278">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C278" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D278" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E278" t="s">
-        <v>10</v>
-      </c>
-      <c r="F278">
+        <v>9</v>
+      </c>
+      <c r="F278" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8525,7 +8761,7 @@
         <v>12</v>
       </c>
       <c r="C279" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D279" t="s">
         <v>7</v>
@@ -8533,8 +8769,8 @@
       <c r="E279" t="s">
         <v>10</v>
       </c>
-      <c r="F279">
-        <v>3.0251083997176502E-4</v>
+      <c r="F279" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="280" spans="2:6" x14ac:dyDescent="0.25">
@@ -8542,16 +8778,16 @@
         <v>12</v>
       </c>
       <c r="C280" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D280" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E280" t="s">
         <v>10</v>
       </c>
-      <c r="F280">
-        <v>2.0167389331450999E-4</v>
+      <c r="F280" s="5">
+        <v>1.0083694665725499E-4</v>
       </c>
     </row>
     <row r="281" spans="2:6" x14ac:dyDescent="0.25">
@@ -8567,7 +8803,7 @@
       <c r="E281" t="s">
         <v>10</v>
       </c>
-      <c r="F281">
+      <c r="F281" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8584,7 +8820,7 @@
       <c r="E282" t="s">
         <v>9</v>
       </c>
-      <c r="F282">
+      <c r="F282" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8601,7 +8837,7 @@
       <c r="E283" t="s">
         <v>9</v>
       </c>
-      <c r="F283">
+      <c r="F283" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8618,7 +8854,7 @@
       <c r="E284" t="s">
         <v>9</v>
       </c>
-      <c r="F284">
+      <c r="F284" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8635,7 +8871,7 @@
       <c r="E285" t="s">
         <v>10</v>
       </c>
-      <c r="F285">
+      <c r="F285" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
@@ -8652,7 +8888,7 @@
       <c r="E286" t="s">
         <v>10</v>
       </c>
-      <c r="F286">
+      <c r="F286" s="5">
         <v>1.0083694665725499E-4</v>
       </c>
     </row>
